--- a/docs/FCC-core-55-70/FCC-core-PRD-v1.1-2026-07-01.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-PRD-v1.1-2026-07-01.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" style="24" min="1" max="1"/>
@@ -1291,6 +1291,87 @@
       <c r="E16" s="28" t="inlineStr">
         <is>
           <t>PRD text updated where it conflicted (Sameness contract row); the detailed design is the authoritative spec for both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="84" customHeight="1" s="24">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>Erratum · F10 scope</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>v1 scope narrowed at detailed design: the scam flag watches CONNECTED-account money-out transactions only — hand-typed entries are never flagged (you don't interrogate someone about a number they just told you). v1 rules = unusually-large vs the account's typical, first-time payee, 3+ same-day money-outs ≥ $1,000; the 'apparent duplicate' rule is deferred beyond v1.</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>Recorded from the strategy-traceability review; the detailed design is the authoritative spec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="84" customHeight="1" s="24">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Erratum · income fields</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>ri_* amounts gain a dedicated edit surface — the new 'Your monthly income' screen (Cash flow tab) — plus net-new fields: ri_*_month (which month an annual/quarterly source lands), ri_*_day (arrival day, optional), and a per-source 'receiving now' flag, all feeding the F5 dated placement.</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>Recorded from the strategy-traceability review; the detailed design is the authoritative spec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="84" customHeight="1" s="24">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Erratum · F5 guaranteed</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>F5 'guaranteed income' = ri_ss + ri_pension + ri_annuities + ri_other, received-now only; ri_withdrawals and ri_rmd are EXCLUDED — the solved safe draw and the pinned required withdrawal replace them, so no savings-draw is ever counted twice in the paycheck. The B-31 snapshot pin aligns to this definition.</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>Recorded from the strategy-traceability review; the detailed design is the authoritative spec.</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-PRD-v1.1-2026-07-01.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-PRD-v1.1-2026-07-01.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Calculation catalog" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Sameness contract" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="NFR · data integrity · Plaid" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Amendments v1.1→v1.2" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Acceptance criteria'!$A$1:$D$171</definedName>
@@ -834,6 +835,158 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" style="24" min="1" max="1"/>
+    <col width="30" customWidth="1" style="24" min="2" max="2"/>
+    <col width="95" customWidth="1" style="24" min="3" max="3"/>
+    <col width="40" customWidth="1" style="24" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>New/changed acceptance criteria</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F2 Debt — repayment shapes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Debt.payment_type ∈ installment | revolving | due_in_full, USER-EDITABLE via the one DebtEditorSheet ("How is it repaid?"). Installment: real payment ↔ paid-off-by, either computed (monthsToClear/paymentToClearBy); saves min=payment. Due-in-full: amount+date → ONE dated big-ticket in the grid + bill calendar + Later; zero monthly obligation in DTI/cash flow; balance still in net worth; payoffPlan clears it in its due month. Deferred loans: first_payment_date captured in the installment shape ("Payments start").</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Founder-approved 2026-07-31 (mock debt-editor-v1); B47 finding 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>F6/F9 Big one-time costs</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NEW: bigCosts[] {label, amount(today $), year} captured on /big-costs; simulate() subtracts each, inflated to its year, accumulation AND decumulation; the capture screen states the odds delta via the SAME selector; empty state = "odds assume none". Hub row "What big costs are coming?" both lenses.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Founder-approved 2026-08-01/02 (mock big-costs-v1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>F11 Plan hub — dynamic door + next decision</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>First-day door counts ONLY missing answers (age/spend/have) and credits live accounts ("already in: N connected accounts, $X counted"). ONE dated next-decision card: RMD-due-untaken outranks SS-window; absent when nothing due. RULE SOURCE: nextDecision (domain/planning/hub.ts) — F10 #14/#15 insights MUST derive from the same helpers, never re-implement.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Founder-approved mock v9 (2026-08-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>F7 Net worth — by-type grouping</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>All CASH-bucket kinds merge under ONE "Cash and cash equivalents" group header (CASH_GROUP_LABEL); rows keep their own names. Class list orders by liquidity: Cash → Bonds &amp; CDs → Stocks/ETFs → Alternatives → property.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>B47 finding 14 + approved mocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F1 Connect — provider</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SnapTrade remains the shipping provider. Founder evaluating Plaid vs SnapTrade vs Teller (pivot ON HOLD 2026-08-02); credit-card transaction import is a design-first candidate pending the provider decision.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Founder provider review</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/FCC-core-55-70/FCC-core-PRD-v1.1-2026-07-01.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-PRD-v1.1-2026-07-01.xlsx
@@ -841,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="24" min="1" max="1"/>
@@ -979,6 +979,28 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>Founder provider review</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Asset classification (F1)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMENDMENT (founder 2026-08-04): cash = cash ONLY (checking/savings/HYSA/cash-mgmt/sweep). Money-market FUNDS class as Stocks/ETFs (dividend-paying funds, measured); CDs and T-bills class as Bonds &amp; CDs regardless of maturity (interest-paying, measured). Supersedes: money-market=cash (2026-07-19 live-verify mapping) and the build-34 #8 12-month CD split. Rationale: instruments that pay dividends/interest must live inside the Performance-measured buckets or earned-income and return calculations are silently wrong. Broker cash-sleeve dedupe unchanged (keyed on the cash_equivalent flag, not class).</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BUILT 2026-08-04 (sync/import/capture/kind-map/glossary + engine: CD interest = balance × stated rate); 20+ pins rewritten; suite 1,396 green.</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-PRD-v1.1-2026-07-01.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-PRD-v1.1-2026-07-01.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Sameness contract" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="NFR · data integrity · Plaid" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Amendments v1.1→v1.2" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Retirement odds — assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Acceptance criteria'!$A$1:$D$171</definedName>
@@ -29,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,8 +76,16 @@
       <color rgb="FF1A5632"/>
       <sz val="10.5"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -131,6 +140,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1A5632"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00085041"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DFF2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAEEDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -216,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -303,6 +327,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -844,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="24" min="1" max="1"/>
@@ -1032,6 +1063,1211 @@
       <c r="D8" s="31" t="inlineStr">
         <is>
           <t>Founder rule 2026-08-11. Root cause: the missing-data banner printed "Vanguard last updated Aug 3" TWICE for two different accounts because accounts were named by institution alone; and connected accounts wore the broker's verbose wording ("Vanguard Kamala Kavadia Brokerage").</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>F6/F9 Retirement odds — method &amp; assumptions</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>NEW TAB "Retirement odds — assumptions": every input the Monte Carlo runs on, its value, its source, and whether the user can change it. CHANGED: portfolio volatility is now measured per asset class from the same long-run series as the returns (KIND_VOLATILITY + blendedVolatility), replacing the derived "return × 1.7" rule which called a savings account 5% volatile and could not distinguish bonds from shares. The old rule remains only as the scenario fallback when a return is typed with nothing held. ALSO: the retirement info dot now explains the whole method and every one of these numbers in plain English, and names the screen that changes them.</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-11: "where are we getting data or assumptions for monte carlo simulation?" → fix the weak assumption, explain it to a non-finance reader, and record it in the master PRD.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" style="24" min="1" max="1"/>
+    <col width="30" customWidth="1" style="24" min="2" max="2"/>
+    <col width="92" customWidth="1" style="24" min="3" max="3"/>
+    <col width="26" customWidth="1" style="24" min="4" max="4"/>
+    <col width="34" customWidth="1" style="24" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" s="24">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B1" s="32" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="32" t="inlineStr">
+        <is>
+          <t>Where it comes from / what it means</t>
+        </is>
+      </c>
+      <c r="D1" s="32" t="inlineStr">
+        <is>
+          <t>User can change?</t>
+        </is>
+      </c>
+      <c r="E1" s="32" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>METHOD</t>
+        </is>
+      </c>
+      <c r="B2" s="33" t="inlineStr"/>
+      <c r="C2" s="33" t="inlineStr"/>
+      <c r="D2" s="33" t="inlineStr"/>
+      <c r="E2" s="33" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>Simulation type</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>Monte Carlo — 500 independent paths</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>Each path plays the whole plan year by year: growth while working, then drawdown to the horizon. A path SUCCEEDS if the balance never reaches zero.</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E3" s="31" t="inlineStr">
+        <is>
+          <t>simulate() · domain/retirement/index.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>The probability</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>successes ÷ 500, rounded to a whole percent</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>If the money lasts in 420 of 500 paths, the odds read 84%.</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>chance_of_success</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>Yearly return draw</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Normal distribution (Box–Muller) around the mean return, spread by the volatility</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Each simulated year draws its own return. This is what makes the 500 paths differ.</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>normal(rng, mean, sd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>Randomness</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Seeded (seed 12345) — deterministic</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>The same inputs always give the same odds, so the number never jitters between visits. Only changing an assumption changes it.</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>mulberry32(seed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>Verdict words</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>≥80% Likely · 60–79% Uncertain · &lt;60% Unlikely (retired: Holding · Watch closely · Running short)</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>The word pairs the number so colour is never the only signal.</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>lensChanceWord / chanceWord</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>GROWTH — annual, nominal, before inflation</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr"/>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>Weighted across YOUR holdings by the amount earmarked for retirement — never one flat rate.</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr"/>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>blendedReturn(accounts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>Shares / ETFs</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>10.4%</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 total return, 30-year</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Yes — Plan → Retirement</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>ASSET_KINDS.ret</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>401(k) / Traditional IRA / Roth IRA / HSA</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>7.9%</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Assumed 60/40 mix, 30-year (ESTIMATE)</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>ASSET_KINDS.ret</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>Brokerage (mix unknown)</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>8.0%</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Blended taxable portfolio (ESTIMATE)</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>ASSET_KINDS.ret</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Bonds &amp; CDs / fixed income</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>US Aggregate Bond index, 30-year</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>ASSET_KINDS.ret</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>High-yield savings · money market · CD · cash management</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>4.2% · 4.5% · 4.2% · 3.5%</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>Current rates (ESTIMATE)</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>ASSET_KINDS.ret</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>Savings · checking</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>2.4% · 0.5%</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>3-month Treasury bill, 30-year · interest checking (ESTIMATE)</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>ASSET_KINDS.ret</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>Gold / commodities</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>8.2%</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Gold (SPDR GLD), 30-year</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>ASSET_KINDS.ret</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>Private equity · hedge funds</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>13% · 6%</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>Cambridge Associates US PE ~25-yr · HFRI Fund Weighted ~10-yr (both ESTIMATES)</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E16" s="31" t="inlineStr">
+        <is>
+          <t>ASSET_KINDS.ret</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>NO long-run benchmark exists — a placeholder the user should set (ESTIMATE)</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>ASSET_KINDS.ret</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>Home · vehicle</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>4.5% · −5%</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>Case-Shiller US home price, 30-yr · vehicle depreciation (ESTIMATE). Property is excluded from the nest egg.</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>ASSET_KINDS.ret</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Nothing held yet</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>Fallback so a plan can still be simulated before any account exists</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>blendedReturn fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>THE UPS AND DOWNS — annual standard deviation</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr"/>
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>ADDED 2026-08-11. Was previously derived as return × 1.7 (floored 5%) — a rule of thumb that called a savings account 5% volatile and could not tell bonds from shares.</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr"/>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>blendedVolatility(accounts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>Shares / ETFs</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>±18%</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 annual std dev, 30-year</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>No (derived from holdings)</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>KIND_VOLATILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>401(k) / IRA / Roth / HSA</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>±11%</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>60/40 mix annual std dev, 30-year (ESTIMATE)</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>KIND_VOLATILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>Brokerage</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>±14%</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>Blended taxable portfolio (ESTIMATE)</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>KIND_VOLATILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>Bonds &amp; CDs</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>±6%</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>US Aggregate Bond index annual std dev</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>KIND_VOLATILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>Cash (checking · savings · HYSA · MMF · CD)</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>±0.5% to ±1.2%</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>3-month Treasury bill annual std dev</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>KIND_VOLATILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Gold / commodities · private equity · hedge funds</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>±16% · ±20% · ±8%</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>Same series as their returns. PE is SMOOTHED — its true swing is wider (ESTIMATE).</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>KIND_VOLATILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>±70%</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>No long-run series — a deliberately wide placeholder (ESTIMATE)</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>KIND_VOLATILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>±10%</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>Case-Shiller annual std dev</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>KIND_VOLATILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>Nothing held yet</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="inlineStr">
+        <is>
+          <t>±12%</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>Fallback; the scenario sliders instead derive volatility from the typed return (return × 1.7, clamped 5–20%)</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>volOf() — scenario only</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>YOUR ANSWERS</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr"/>
+      <c r="C30" s="33" t="inlineStr"/>
+      <c r="D30" s="33" t="inlineStr"/>
+      <c r="E30" s="33" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t>2.5% a year</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>Default; raises spending AND Social Security over time</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
+        <is>
+          <t>Yes — Plan → Retirement</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>inflationRate</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>Retirement age</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>Your answer, else 65</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>A retiree is simulated from today</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
+        <is>
+          <t>targetRetirementAge / assumptions.retireAge</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>Plan-to age (horizon)</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="inlineStr">
+        <is>
+          <t>Your answer, else 90</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>The age the money must reach</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>horizonAge</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>Monthly spending in retirement</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>Your answer, else today's spending, else $5,000</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="inlineStr">
+        <is>
+          <t>Inflated to the retirement year, then each year after</t>
+        </is>
+      </c>
+      <c r="D34" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>retirementSpendMonthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>Social Security / pension</t>
+        </is>
+      </c>
+      <c r="B35" s="31" t="inlineStr">
+        <is>
+          <t>Your captured amount, adjusted for claim age</t>
+        </is>
+      </c>
+      <c r="C35" s="31" t="inlineStr">
+        <is>
+          <t>Counted only FROM the claim age — 67 unless chosen otherwise</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="inlineStr">
+        <is>
+          <t>Yes — Plan → Social Security timing</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>ssBenefitAtClaimAge</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t>Contributions</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>From your onboarding answers, grown yearly</t>
+        </is>
+      </c>
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>Added each working year</t>
+        </is>
+      </c>
+      <c r="D36" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>monthlyContributionsFromOnboarding</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>Nest egg</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="inlineStr">
+        <is>
+          <t>Retirement-EARMARKED balances only</t>
+        </is>
+      </c>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>Cash and property default to 0% earmarked; investment and retirement accounts to 100%. Per-account override available.</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="inlineStr">
+        <is>
+          <t>Yes — per account</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
+        <is>
+          <t>retirementEarmarkedValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t>TAX &amp; RULES INSIDE THE SIMULATION</t>
+        </is>
+      </c>
+      <c r="B38" s="33" t="inlineStr"/>
+      <c r="C38" s="33" t="inlineStr"/>
+      <c r="D38" s="33" t="inlineStr"/>
+      <c r="E38" s="33" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t>Required withdrawals (RMD)</t>
+        </is>
+      </c>
+      <c r="B39" s="31" t="inlineStr">
+        <is>
+          <t>From age 73, IRS divisor by age</t>
+        </is>
+      </c>
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>Forced out of the pre-tax slice; the NET stays in the pot</t>
+        </is>
+      </c>
+      <c r="D39" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E39" s="31" t="inlineStr">
+        <is>
+          <t>RMD_START_AGE_SIM / rmdDivisorSim</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>Tax on required withdrawals</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>22% of the RMD leaves the pot</t>
+        </is>
+      </c>
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>Default effective rate; the pre-tax share is computed from the actual account mix</t>
+        </is>
+      </c>
+      <c r="D40" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E40" s="31" t="inlineStr">
+        <is>
+          <t>rmd_tax_rate · pre_tax_share</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>Big one-time costs</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="inlineStr">
+        <is>
+          <t>Your captured costs, in the year given</t>
+        </is>
+      </c>
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>Inflated from today's dollars to their year; costs outside the horizon are ignored</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="inlineStr">
+        <is>
+          <t>Yes — Plan → Big costs</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>one_off_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="31" t="inlineStr">
+        <is>
+          <t>"Needed" figure (the gap)</t>
+        </is>
+      </c>
+      <c r="B42" s="31" t="inlineStr">
+        <is>
+          <t>25 × net annual spend</t>
+        </is>
+      </c>
+      <c r="C42" s="31" t="inlineStr">
+        <is>
+          <t>The 4% rule, applied to spending net of guaranteed income. Used for the gap and the suggested extra monthly saving, NOT for the odds.</t>
+        </is>
+      </c>
+      <c r="D42" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E42" s="31" t="inlineStr">
+        <is>
+          <t>needed = spend × 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="33" t="inlineStr">
+        <is>
+          <t>HONEST LIMITS — stated in the info dot too</t>
+        </is>
+      </c>
+      <c r="B43" s="33" t="inlineStr"/>
+      <c r="C43" s="33" t="inlineStr"/>
+      <c r="D43" s="33" t="inlineStr"/>
+      <c r="E43" s="33" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="34" t="inlineStr">
+        <is>
+          <t>Independent years</t>
+        </is>
+      </c>
+      <c r="B44" s="34" t="inlineStr">
+        <is>
+          <t>Each year's return is drawn independently</t>
+        </is>
+      </c>
+      <c r="C44" s="34" t="inlineStr">
+        <is>
+          <t>Real markets cluster — bad years arrive together, and clustering early in retirement is what breaks a plan (sequence-of-returns risk). Independent draws make the odds slightly BETTER than reality for someone about to retire.</t>
+        </is>
+      </c>
+      <c r="D44" s="34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E44" s="34" t="inlineStr">
+        <is>
+          <t>Known limitation</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="34" t="inlineStr">
+        <is>
+          <t>Holdings move together</t>
+        </is>
+      </c>
+      <c r="B45" s="34" t="inlineStr">
+        <is>
+          <t>Volatility is a weighted average across holdings</t>
+        </is>
+      </c>
+      <c r="C45" s="34" t="inlineStr">
+        <is>
+          <t>This ignores diversification, so it slightly OVERSTATES risk — the odds come out cautious rather than flattering. The opposite side of the previous limit.</t>
+        </is>
+      </c>
+      <c r="D45" s="34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E45" s="34" t="inlineStr">
+        <is>
+          <t>blendedVolatility</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="34" t="inlineStr">
+        <is>
+          <t>Not a promise</t>
+        </is>
+      </c>
+      <c r="B46" s="34" t="inlineStr">
+        <is>
+          <t>An estimate from your numbers and these assumptions</t>
+        </is>
+      </c>
+      <c r="C46" s="34" t="inlineStr">
+        <is>
+          <t>Every figure above is visible to the user in the retirement info dot, in plain English, with the screen that changes it.</t>
+        </is>
+      </c>
+      <c r="D46" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="34" t="inlineStr">
+        <is>
+          <t>GLOSSARY.nestEggMath</t>
         </is>
       </c>
     </row>
